--- a/data/trans_dic/P17A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P17A-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 14,43</t>
+          <t>8,67; 14,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 16,56</t>
+          <t>10,02; 16,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,73</t>
+          <t>12,75; 20,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 14,62</t>
+          <t>3,69; 11,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 21,99</t>
+          <t>14,81; 22,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 27,22</t>
+          <t>18,61; 27,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,27; 27,88</t>
+          <t>19,61; 27,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 24,45</t>
+          <t>13,4; 24,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,59; 17,11</t>
+          <t>12,39; 17,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 20,52</t>
+          <t>15,33; 20,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,58</t>
+          <t>17,07; 22,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 16,42</t>
+          <t>9,27; 16,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,48</t>
+          <t>7,89; 12,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,61</t>
+          <t>12,2; 17,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,63</t>
+          <t>12,13; 18,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 24,13</t>
+          <t>13,05; 21,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 27,89</t>
+          <t>20,52; 27,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,28; 30,64</t>
+          <t>23,51; 30,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,45; 31,91</t>
+          <t>24,31; 31,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,91; 59,45</t>
+          <t>18,71; 26,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,52</t>
+          <t>14,49; 18,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 22,91</t>
+          <t>18,09; 22,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 24,21</t>
+          <t>19,08; 23,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,32; 44,78</t>
+          <t>16,94; 22,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,81</t>
+          <t>11,83; 17,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 22,13</t>
+          <t>16,05; 22,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 25,22</t>
+          <t>18,65; 25,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,36</t>
+          <t>11,87; 18,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,68; 30,44</t>
+          <t>23,83; 30,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,97; 30,88</t>
+          <t>23,95; 30,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,84</t>
+          <t>22,86; 29,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 24,73</t>
+          <t>18,97; 24,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 23,38</t>
+          <t>18,79; 23,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,96; 25,54</t>
+          <t>21,07; 25,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,77; 26,73</t>
+          <t>22,01; 26,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,36; 20,76</t>
+          <t>16,11; 20,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 19,31</t>
+          <t>12,61; 19,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,06</t>
+          <t>15,49; 21,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 29,34</t>
+          <t>22,48; 29,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,75</t>
+          <t>16,71; 23,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,03; 32,43</t>
+          <t>24,63; 32,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,5; 35,46</t>
+          <t>27,73; 35,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,57; 31,52</t>
+          <t>24,17; 31,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,05; 26,69</t>
+          <t>21,91; 26,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,72; 24,71</t>
+          <t>19,38; 24,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,87</t>
+          <t>22,4; 27,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 29,43</t>
+          <t>24,3; 29,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 22,69</t>
+          <t>20,25; 24,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,1; 37,09</t>
+          <t>28,49; 37,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,15; 35,45</t>
+          <t>25,8; 35,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,25; 34,74</t>
+          <t>25,9; 34,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,65; 28,17</t>
+          <t>19,98; 26,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,45; 42,23</t>
+          <t>32,47; 41,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,14; 40,52</t>
+          <t>31,63; 40,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,75; 43,91</t>
+          <t>34,64; 44,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,96; 28,31</t>
+          <t>23,25; 28,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,83; 38,28</t>
+          <t>31,74; 38,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,21; 36,53</t>
+          <t>30,15; 36,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,62; 38,39</t>
+          <t>31,7; 38,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 27,3</t>
+          <t>22,72; 27,07</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,57; 51,86</t>
+          <t>40,66; 52,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,44; 50,04</t>
+          <t>37,75; 49,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,35; 44,21</t>
+          <t>33,82; 44,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,85; 32,21</t>
+          <t>24,68; 32,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,31; 52,51</t>
+          <t>42,26; 52,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,24; 48,94</t>
+          <t>38,29; 48,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,78; 54,7</t>
+          <t>43,86; 54,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,78; 31,75</t>
+          <t>27,76; 34,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,98; 50,47</t>
+          <t>42,89; 50,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40,07; 47,86</t>
+          <t>39,75; 47,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,82; 48,48</t>
+          <t>40,67; 48,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,33; 30,06</t>
+          <t>27,26; 32,06</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,31; 51,18</t>
+          <t>37,99; 51,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,36; 52,52</t>
+          <t>38,75; 52,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,91; 47,71</t>
+          <t>36,82; 47,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,3; 32,74</t>
+          <t>24,75; 33,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,9; 56,01</t>
+          <t>44,4; 56,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,32; 54,0</t>
+          <t>44,13; 54,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,39; 49,79</t>
+          <t>38,16; 49,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,06; 33,4</t>
+          <t>28,01; 34,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43,54; 52,04</t>
+          <t>43,15; 52,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,22; 52,28</t>
+          <t>44,08; 52,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,01; 47,47</t>
+          <t>38,58; 47,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,81; 31,94</t>
+          <t>27,58; 32,79</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,43</t>
+          <t>18,79; 21,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,39; 24,38</t>
+          <t>21,36; 24,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,57; 26,71</t>
+          <t>23,88; 26,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,61</t>
+          <t>18,19; 21,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,43</t>
+          <t>29,46; 32,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,22</t>
+          <t>30,99; 34,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,33; 34,63</t>
+          <t>31,38; 34,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,74; 28,71</t>
+          <t>23,62; 26,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,69; 26,78</t>
+          <t>24,59; 26,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,86; 28,95</t>
+          <t>26,72; 28,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,98; 30,13</t>
+          <t>28,02; 30,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 24,15</t>
+          <t>21,32; 23,19</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>65113</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>93347</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42643; 71175</t>
+          <t>42755; 71776</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45329; 75054</t>
+          <t>45408; 74304</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55047; 82749</t>
+          <t>53479; 84297</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15629; 58490</t>
+          <t>15049; 47839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70947; 102802</t>
+          <t>69220; 103268</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81477; 115941</t>
+          <t>79293; 115596</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76264; 110327</t>
+          <t>77611; 110138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38519; 76571</t>
+          <t>48588; 87945</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120971; 164383</t>
+          <t>119016; 163896</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133375; 180358</t>
+          <t>134805; 179424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139654; 184044</t>
+          <t>139150; 184870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62951; 117097</t>
+          <t>71390; 127397</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>81752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>166114</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>244758</t>
+          <t>192536</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56760; 91692</t>
+          <t>57951; 90123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83223; 120341</t>
+          <t>83347; 120186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73768; 110017</t>
+          <t>71649; 109451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59413; 102201</t>
+          <t>62255; 103864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>130329; 174434</t>
+          <t>128375; 174991</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>141665; 186436</t>
+          <t>143020; 187167</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>137794; 179825</t>
+          <t>136975; 180096</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106692; 303343</t>
+          <t>93317; 131971</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195406; 251860</t>
+          <t>197142; 251358</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>233980; 295882</t>
+          <t>233662; 293406</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>222443; 279353</t>
+          <t>220237; 276171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>180437; 418175</t>
+          <t>165240; 224323</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80701</t>
+          <t>92110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>118499</t>
+          <t>134536</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>199199</t>
+          <t>226646</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77125; 113741</t>
+          <t>75554; 112891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107573; 150032</t>
+          <t>108811; 152132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126468; 168759</t>
+          <t>124755; 168968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64430; 98447</t>
+          <t>73701; 111818</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>162877; 209321</t>
+          <t>163918; 210722</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>169914; 218947</t>
+          <t>169770; 217213</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>152403; 197375</t>
+          <t>151206; 196301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>103545; 134135</t>
+          <t>118029; 152229</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>252212; 310101</t>
+          <t>249281; 311258</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290772; 354241</t>
+          <t>292256; 354964</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>289625; 355699</t>
+          <t>292825; 353156</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>176488; 223961</t>
+          <t>200245; 256565</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>140816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>167846</t>
+          <t>178541</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>294854</t>
+          <t>319357</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66771; 100222</t>
+          <t>65474; 99447</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94231; 135609</t>
+          <t>95193; 135119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>144412; 189582</t>
+          <t>145203; 191280</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57687; 184240</t>
+          <t>117061; 164674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129049; 167248</t>
+          <t>127014; 169313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>169161; 218128</t>
+          <t>170546; 218134</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159465; 204570</t>
+          <t>156857; 203771</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>142879; 190172</t>
+          <t>161380; 197852</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>204064; 255746</t>
+          <t>200541; 256647</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>276238; 342699</t>
+          <t>275469; 338363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>315835; 381129</t>
+          <t>314766; 383442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>178891; 363089</t>
+          <t>290960; 349762</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138635</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>157809</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>277047</t>
+          <t>299931</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>108669; 143427</t>
+          <t>110172; 144834</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111502; 151174</t>
+          <t>110004; 151074</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125450; 166033</t>
+          <t>123778; 164286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121486; 158114</t>
+          <t>121734; 163015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131086; 170596</t>
+          <t>131183; 169427</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>139433; 181435</t>
+          <t>141622; 182557</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>172640; 218148</t>
+          <t>172111; 220633</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>125720; 155008</t>
+          <t>141436; 174569</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>251686; 302648</t>
+          <t>250991; 302822</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>264106; 319357</t>
+          <t>263571; 322059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>308239; 374244</t>
+          <t>309001; 373595</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>252790; 302719</t>
+          <t>276646; 329628</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104761</t>
+          <t>115706</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>227159</t>
+          <t>250987</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>118325; 151259</t>
+          <t>118591; 152673</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>118700; 154517</t>
+          <t>116565; 154238</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114836; 147797</t>
+          <t>113068; 150066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91320; 118373</t>
+          <t>100316; 131915</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>145081; 180077</t>
+          <t>144934; 179778</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>134970; 172763</t>
+          <t>135154; 172135</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>165386; 206634</t>
+          <t>165675; 205384</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47256; 192846</t>
+          <t>121639; 150571</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>272713; 320265</t>
+          <t>272160; 321999</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>265168; 316714</t>
+          <t>263038; 313998</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290656; 345240</t>
+          <t>289593; 341980</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>110506; 293100</t>
+          <t>230226; 270778</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>128234</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>208630</t>
+          <t>234440</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>78308; 107413</t>
+          <t>79733; 107498</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>97894; 130610</t>
+          <t>96370; 130908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94870; 122601</t>
+          <t>94630; 123290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>68503; 92305</t>
+          <t>76542; 103534</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>146584; 187024</t>
+          <t>148255; 187116</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>168079; 209505</t>
+          <t>171208; 210521</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>153628; 199227</t>
+          <t>152696; 198681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>115124; 142108</t>
+          <t>130041; 160089</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>236748; 282985</t>
+          <t>234656; 283341</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281518; 332859</t>
+          <t>280633; 334093</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>256378; 311948</t>
+          <t>253517; 309360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>189624; 225910</t>
+          <t>213340; 253640</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>610391; 701611</t>
+          <t>615137; 706471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>730173; 831885</t>
+          <t>728996; 833045</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>799914; 906779</t>
+          <t>810478; 907318</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>483831; 712631</t>
+          <t>642263; 746952</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>989297; 1095103</t>
+          <t>994968; 1102982</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1101719; 1213743</t>
+          <t>1099160; 1211669</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1110662; 1227594</t>
+          <t>1112386; 1217719</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>758693; 1050300</t>
+          <t>881086; 972095</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1642244; 1780854</t>
+          <t>1635480; 1776710</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1869143; 2015001</t>
+          <t>1859772; 2011120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1941723; 2090482</t>
+          <t>1944005; 2099412</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1355095; 1718603</t>
+          <t>1547884; 1683892</t>
         </is>
       </c>
     </row>
